--- a/Documentation/Hardware/Second_Stage/Sourcing_Enclosure.xlsx
+++ b/Documentation/Hardware/Second_Stage/Sourcing_Enclosure.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulLinke\Kleinhirn\VSROOT\SETI-HCRO\MouseWithoutBorders\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulLinke\Kleinhirn\VSROOT\SETI-HCRO\Spikes\Documentation\Hardware\Second_Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF60443-F28F-4F45-80AF-A76C6BA1F9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EACF137-626A-4748-B159-ECC92017C358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="108">
   <si>
     <t>Name</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Front Panel Express</t>
+  </si>
+  <si>
+    <t>FrontPanel.fpd</t>
+  </si>
+  <si>
+    <t>BottomPlate.fpd</t>
   </si>
 </sst>
 </file>
@@ -424,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -439,10 +445,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -772,89 +776,89 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="8">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="8">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="8">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" t="s">
         <v>105</v>
       </c>
     </row>
@@ -938,7 +942,7 @@
       <c r="G9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="I9" t="s">
